--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:08</t>
+    <t xml:space="preserve">2026-09-17 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:04</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:55</t>
+    <t xml:space="preserve">2026-10-05 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -636,7 +636,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>244646.62</v>
+        <v>244646.63</v>
       </c>
     </row>
     <row r="7">
@@ -1061,7 +1061,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>135668.12</v>
+        <v>135668.13</v>
       </c>
     </row>
   </sheetData>
